--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/10_eight_bus_radial_grid_2ph_dd_MP_pf_sc_results_0_branch.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/10_eight_bus_radial_grid_2ph_dd_MP_pf_sc_results_0_branch.xlsx
@@ -107,7 +107,7 @@
     <t>Line_2_3-2ph</t>
   </si>
   <si>
-    <t>Line_3_3-1ph</t>
+    <t>Line_3_3-2ph</t>
   </si>
   <si>
     <t>pf_ikss_a_from_ka</t>
